--- a/Расчет_дезсредства_Фоснитацид.xlsx
+++ b/Расчет_дезсредства_Фоснитацид.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Принята типовая норма влажной дезинфекции гладких поверхностей — 0,5 л/м². Замените на норму из инструкции по применению Фоснитацида — весь файл пересчитается. Варианты норм см. на листе «Сценарии норм расхода».</t>
+          <t>Способ обработки — МОЙКА (влажная дезинфекция), подтверждено заказчиком. Принята типовая норма влажной дезинфекции гладких поверхностей 0,5 л/м². Для шероховатых поверхностей (бетон, кирпич) применяется 1,0 л/м² — см. лист «Сценарии норм расхода».</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Норма расхода рабочего раствора на 1 м² — единственный параметр, не заданный в исходных данных. Ниже — потребность на одну обработку всех корпусов при типовых нормах.</t>
+          <t>Способ обработки — мойка (влажная дезинфекция). Рабочий диапазон норм для мойки: 0,3-1,0 л/м². Ниже — потребность на одну обработку всех корпусов при разных нормах.</t>
         </is>
       </c>
     </row>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Ориентировочно соответствует текущей выдаче 1 канистры на корпус</t>
+          <t>Соответствует текущей выдаче 1 канистры на корпус. Аэрозольный режим — НЕ ваш случай</t>
         </is>
       </c>
     </row>
@@ -8657,25 +8657,25 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Аэрозольная / мелкокапельная обработка</t>
+          <t>Аэрозольная / мелкокапельная обработка — НЕ ваш случай</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="24" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="B7" s="25">
         <f>'Расчет по корпусам'!$E$124*A7*'Параметры'!$C$8</f>
-        <v>44432.28999999999</v>
+        <v>53318.74799999999</v>
       </c>
       <c r="C7" s="25">
         <f>B7*'Параметры'!$C$6/100</f>
-        <v>4443.228999999999</v>
+        <v>5331.8748</v>
       </c>
       <c r="D7" s="13">
         <f>SUMPRODUCT(ROUNDUP('Расчет по корпусам'!$E$2:$E$123*$A7*'Параметры'!$C$8*'Параметры'!$C$6/100/'Параметры'!$C$9,0))</f>
-        <v>244</v>
+        <v>299</v>
       </c>
       <c r="E7" s="13">
         <f>'Расчет по корпусам'!$C$124*'Параметры'!$C$10</f>
@@ -8683,71 +8683,71 @@
       </c>
       <c r="F7" s="13">
         <f>E7-D7</f>
-        <v>-122</v>
+        <v>-177</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Аэрозольная обработка, усиленный режим</t>
+          <t>Мойка, минимальный режим</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="B8" s="25">
+      <c r="A8" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B8" s="28">
         <f>'Расчет по корпусам'!$E$124*A8*'Параметры'!$C$8</f>
-        <v>53318.74799999999</v>
-      </c>
-      <c r="C8" s="25">
+        <v>88864.57999999999</v>
+      </c>
+      <c r="C8" s="28">
         <f>B8*'Параметры'!$C$6/100</f>
-        <v>5331.8748</v>
-      </c>
-      <c r="D8" s="13">
+        <v>8886.457999999999</v>
+      </c>
+      <c r="D8" s="16">
         <f>SUMPRODUCT(ROUNDUP('Расчет по корпусам'!$E$2:$E$123*$A8*'Параметры'!$C$8*'Параметры'!$C$6/100/'Параметры'!$C$9,0))</f>
-        <v>299</v>
-      </c>
-      <c r="E8" s="13">
+        <v>453</v>
+      </c>
+      <c r="E8" s="16">
         <f>'Расчет по корпусам'!$C$124*'Параметры'!$C$10</f>
         <v>122</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="16">
         <f>E8-D8</f>
-        <v>-177</v>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>Влажная дезинфекция, минимальный режим</t>
+        <v>-331</v>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>МОЙКА, гладкие поверхности — ПРИНЯТО В РАСЧЕТЕ</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B9" s="28">
+      <c r="A9" s="24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="B9" s="25">
         <f>'Расчет по корпусам'!$E$124*A9*'Параметры'!$C$8</f>
-        <v>88864.57999999999</v>
-      </c>
-      <c r="C9" s="28">
+        <v>133296.87</v>
+      </c>
+      <c r="C9" s="25">
         <f>B9*'Параметры'!$C$6/100</f>
-        <v>8886.457999999999</v>
-      </c>
-      <c r="D9" s="16">
+        <v>13329.687</v>
+      </c>
+      <c r="D9" s="13">
         <f>SUMPRODUCT(ROUNDUP('Расчет по корпусам'!$E$2:$E$123*$A9*'Параметры'!$C$8*'Параметры'!$C$6/100/'Параметры'!$C$9,0))</f>
-        <v>453</v>
-      </c>
-      <c r="E9" s="16">
+        <v>630</v>
+      </c>
+      <c r="E9" s="13">
         <f>'Расчет по корпусам'!$C$124*'Параметры'!$C$10</f>
         <v>122</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="13">
         <f>E9-D9</f>
-        <v>-331</v>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Влажная дезинфекция гладких поверхностей — принято в расчете</t>
+        <v>-508</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Мойка, промежуточный режим</t>
         </is>
       </c>
     </row>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Влажная дезинфекция шероховатых поверхностей / двукратная обработка</t>
+          <t>Мойка шероховатых поверхностей (бетон, кирпич) / двукратная обработка</t>
         </is>
       </c>
     </row>
